--- a/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（$et）.xlsx
+++ b/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（$et）.xlsx
@@ -59,63 +59,100 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;：{$et:&lt;值&gt;}}查询，目标字段为数值型，覆盖如下数据类型：
+    <t>1、支持数值型值的数据比较
+2、返回等于指定值的记录，返回结果集正确</t>
+  </si>
+  <si>
+    <t>1、支持数值型值的数据比较，且走索引和不走索引结果一致
+2、返回等于指定值的记录，返回结果集正确</t>
+  </si>
+  <si>
+    <t>1、支持嵌套数组的数据比较
+2、返回等于指定值的记录，返回结果集正确</t>
+  </si>
+  <si>
+    <t>1、支持嵌套数组的数据比较，且走索引和不走索引结果一致
+2、返回等于指定值的记录，返回结果集正确</t>
+  </si>
+  <si>
+    <t>1、支持非数值型的数据比较
+2、返回等于指定值的记录，返回结果集正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、支持非数值型的数据比较，且走索引和不走索引结果一致
+2、返回等于指定值的记录，返回结果集正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、查询成功，返回等于指定值的记录，返回结果集正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$et查询，目标字段为数值型，不走索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$et查询，目标字段为数值型，走索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$et查询，目标字段为数组且元素为数值型，不走索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$et查询，目标字段为数组且元素为数值型，走索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$et查询，目标字段为非数值型，不走索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$et查询，目标字段为非数值型，走索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$et查询，目标字段与给定值为不同类型，不走索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用$et查询，目标字段与给定值为不同类型，走索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$et:&lt;值&gt;}})查询，目标字段为数值型，覆盖如下数据类型：
 int/long/double，且包含该类型的最大和最小边界
 指定的$et的值覆盖每种类型的最大和最小边界
 2、检查查询结果正确性</t>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;：{$et:&lt;值&gt;}}查询，目标字段为数值型，且为索引字段，覆盖如下数据类型：
+    <t>1、find({&lt;字段名&gt;：{$et:&lt;值&gt;}})查询，目标字段为数值型，且为索引字段，覆盖如下数据类型：
 int/long/double，且包含该类型的最大和最小边界
 指定的$et的值覆盖每种类型的最大和最小边界
 2、检查查询结果正确性</t>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;：{$et:&lt;值&gt;}}查询，目标字段为嵌套数组，数组元素包含数值型（int/long/double），$et指定的字段名为"a"或"a.b"表示
+    <t>1、find({&lt;字段名&gt;：{$et:&lt;值&gt;}})查询，目标字段为嵌套数组，数组元素包含数值型（int/long/double），$et指定的字段名为"a"或"a.b"表示
 2、检查查询结果正确性</t>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;：{$et:&lt;值&gt;}}查询，目标字段为嵌套数组，且为索引字段，数组元素包含数值型（int/long/double），$et指定的字段名为"a"或"a.b"表示
+    <t>1、find({&lt;字段名&gt;：{$et:&lt;值&gt;}})查询，目标字段为嵌套数组，且为索引字段，数组元素包含数值型（int/long/double），$et指定的字段名为"a"或"a.b"表示
 2、检查查询结果正确性</t>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;：{$et:&lt;值&gt;}}查询，目标字段为非数值型，覆盖其他所有非数值型数据：
+    <t>1、find({&lt;字段名&gt;：{$et:&lt;值&gt;}})查询，目标字段为非数值型，覆盖其他所有非数值型数据：
 null, string, bool, array, oid, date, binary, regex, timestamp, minKey, maxKey, subobj
 2、检查查询结果正确性</t>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;：{$et:&lt;值&gt;}}查询，目标字段为非数值型，且为索引字段，覆盖其他所有非数值型数据：
+    <t>1、find({&lt;字段名&gt;：{$et:&lt;值&gt;}})查询，目标字段为非数值型，且为索引字段，覆盖其他所有非数值型数据：
 null, string, bool, array, oid, date, binary, regex, timestamp, minKey, maxKey, subobj
 2、检查查询结果正确性</t>
-  </si>
-  <si>
-    <t>1、支持数值型值的数据比较
-2、返回等于指定值的记录，返回结果集正确</t>
-  </si>
-  <si>
-    <t>1、支持数值型值的数据比较，且走索引和不走索引结果一致
-2、返回等于指定值的记录，返回结果集正确</t>
-  </si>
-  <si>
-    <t>1、支持嵌套数组的数据比较
-2、返回等于指定值的记录，返回结果集正确</t>
-  </si>
-  <si>
-    <t>1、支持嵌套数组的数据比较，且走索引和不走索引结果一致
-2、返回等于指定值的记录，返回结果集正确</t>
-  </si>
-  <si>
-    <t>1、支持非数值型的数据比较
-2、返回等于指定值的记录，返回结果集正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、支持非数值型的数据比较，且走索引和不走索引结果一致
-2、返回等于指定值的记录，返回结果集正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;：{$et:&lt;值&gt;}}查询，目标字段值与给定值为不同数据类型的数据，覆盖所有数据类型（任意组合覆盖，如：
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$et:&lt;值&gt;}})查询，目标字段值与给定值为不同数据类型的数据，覆盖所有数据类型（任意组合覆盖，如：
 1）int/long/double/bool  
 2）timestamp/date/string  
 3）oid/string  
@@ -126,7 +163,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;：{$et:&lt;值&gt;}}查询，目标字段值与给定值为不同数据类型的数据，且目标字段为索引字段，测试覆盖所有数据类型（任意组合覆盖，如：
+    <t>1、find({&lt;字段名&gt;：{$et:&lt;值&gt;}})查询，目标字段值与给定值为不同数据类型的数据，且目标字段为索引字段，测试覆盖所有数据类型（任意组合覆盖，如：
 1）int/long/double/bool  
 2）timestamp/date/string  
 3）oid/string  
@@ -134,42 +171,6 @@
 5）minKey/maxKey  
 6）null/binary/regex  ）
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、查询成功，返回等于指定值的记录，返回结果集正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$et查询，目标字段为数值型，不走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$et查询，目标字段为数值型，走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$et查询，目标字段为数组且元素为数值型，不走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$et查询，目标字段为数组且元素为数值型，走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$et查询，目标字段为非数值型，不走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$et查询，目标字段为非数值型，走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$et查询，目标字段与给定值为不同类型，不走索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用$et查询，目标字段与给定值为不同类型，走索引查询</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -693,7 +694,7 @@
     </row>
     <row r="2" spans="1:9" ht="67.5">
       <c r="A2" s="5" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>10</v>
@@ -711,10 +712,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="I2" s="3">
         <v>1</v>
@@ -722,7 +723,7 @@
     </row>
     <row r="3" spans="1:9" ht="67.5">
       <c r="A3" s="5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -737,10 +738,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="I3" s="3">
         <v>1</v>
@@ -748,7 +749,7 @@
     </row>
     <row r="4" spans="1:9" ht="54">
       <c r="A4" s="5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
@@ -763,10 +764,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
@@ -774,7 +775,7 @@
     </row>
     <row r="5" spans="1:9" ht="67.5">
       <c r="A5" s="5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
@@ -789,10 +790,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -800,7 +801,7 @@
     </row>
     <row r="6" spans="1:9" ht="67.5">
       <c r="A6" s="5" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>9</v>
@@ -815,10 +816,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
@@ -826,7 +827,7 @@
     </row>
     <row r="7" spans="1:9" ht="67.5">
       <c r="A7" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
@@ -841,10 +842,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="I7" s="3">
         <v>1</v>
@@ -852,7 +853,7 @@
     </row>
     <row r="8" spans="1:9" ht="135">
       <c r="A8" s="6" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>9</v>
@@ -867,16 +868,16 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I8" s="3"/>
     </row>
     <row r="9" spans="1:9" ht="135">
       <c r="A9" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>9</v>
@@ -891,10 +892,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I9" s="3"/>
     </row>
